--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -34,8 +34,8 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00F59E0B"/>
-      <sz val="16"/>
+      <color rgb="005a8f7b"/>
+      <sz val="18"/>
     </font>
     <font>
       <b val="1"/>
@@ -43,7 +43,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000A0A0A"/>
+      <color rgb="003d4442"/>
       <sz val="11"/>
     </font>
     <font>
@@ -61,14 +61,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F59E0B"/>
-        <bgColor rgb="00F59E0B"/>
+        <fgColor rgb="005a8f7b"/>
+        <bgColor rgb="005a8f7b"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E7"/>
-        <bgColor rgb="00FFF8E7"/>
+        <fgColor rgb="00F0F7F4"/>
+        <bgColor rgb="00F0F7F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -473,11 +473,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B30"/>
+  <dimension ref="A2:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>كيف تعدّل البيانات وتحدّث الموقع؟</t>
+          <t>طريقة التعديل والتحديث (خطوة بخطوة)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>حمّل هذا الملف من GitHub (زر Download أو من صفحة الملف).</t>
+          <t>حمّل هذا الملف من GitHub (افتح الملف ثم زر Download).</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>افتحه في برنامج Excel وعدّل البيانات كما تريد (أضف/حذف/عدّل).</t>
+          <t>افتحه في برنامج Excel وعدّل أو أضف البيانات كما تريد.</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ارفع الملف على GitHub مرة أخرى (Replace / Upload).</t>
+          <t>ارفع الملف على GitHub (بنفس الاسم) ليحل محل القديم.</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>الموقع يتحدّث تلقائياً عند أي زائر - لا حاجة لأي شيء آخر!</t>
+          <t>الموقع يتحدّث تلقائياً عند أي زائر - لا حاجة لأي خطوة أخرى!</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>الأوراق الموجودة في الملف:</t>
+          <t>الأوراق الموجودة (كلها مليئة بأمثلة جاهزة)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>كل المنتجات والعروض (الصنف، السعر، الخصم، الصور، المواصفات).</t>
+          <t>المنتجات والعروض - أضف منتجاً جديداً بسطر جديد.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>أقسام المتجر (الاسم + الأيقونة).</t>
+          <t>أقسام المتجر - أضف قسماً جديداً بسطر جديد.</t>
         </is>
       </c>
     </row>
@@ -625,147 +625,218 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>إعدادات المتجر (واتساب، فودافون، انستاباي، شريط الأخبار...).</t>
+          <t>إعدادات المتجر (واتساب، فودافون، انستاباي).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>الأخبار والإشعارات + سرعة العرض.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>حالات المنتجات (جديد، عرض خاص...).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>قواعد مهمة عند الكتابة:</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
+      <c r="A19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>لا تحذف الصف الأول (العناوين) أبداً.</t>
-        </is>
-      </c>
+          <t>قواعد مهمة عند الكتابة</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>لا تحذف الصف الأول (العناوين) من أي ورقة أبداً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>الحقول اللي فيها أكثر من قيمة (صور، مواصفات، شارات) تُفصل بالرمز | مثل:</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" t="inlineStr">
         <is>
           <t xml:space="preserve">    صورة1 | صورة2 | صورة3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>الصور يجب أن تكون روابط URL كاملة (تبدأ بـ https://).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>تاريخ نهاية العرض اكتبه بصيغة سنة-شهر-يوم مثل: 2026-12-31</t>
+          <t>الصور يجب أن تكون روابط URL كاملة تبدأ بـ https://</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>السعر اكتبه رقم فقط بدون رموز.</t>
+          <t>تواريخ نهاية العرض بصيغة سنة-شهر-يوم مثل: 2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>حالة المخزون: اكتب رقم (مثلاً 10) أو كلمة out إذا نفدت الكمية.</t>
+          <t>الأسعار أرقام فقط بدون رموز.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>لا تترك خلايا فارغة في منتصف البيانات - احذف الصف كاملاً لإزالة منتج.</t>
+          <t>المخزون: رقم، أو كلمة out إذا نفدت الكمية.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>لإزالة منتج: احذف الصف كاملاً (لا تترك خلية فارغة).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>بعد التعديل احفظ الملف بصيغة Excel Workbook (.xlsx) وليس CSV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>احفظ الملف بصيغة Excel Workbook (.xlsx) وليس CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>نصيحة: حمّل نسخة احتياطية من الملف قبل أي تعديل كبير.</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="A30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>شرح كل ورقة بالتفصيل</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>كل عمود = معلومة عن المنتج. انسخ صفاً موجوداً وعدّل قيمه لإضافة منتج جديد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>الاسم = اسم القسم، الأيقونة = كود أيقونة مثل fas fa-mobile-alt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>النوع: ticker = شريط الأخبار أعلى الموقع، proof = إشعار الشراء المنبثق. المدة = ثواني العرض.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>المفتاح = اسم الإعداد، القيمة = قيمته. لا تغيّر أسماء المفاتيح.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>نصيحة: احتفظ بنسخة احتياطية من الملف قبل أي تعديل كبير.</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -778,11 +849,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
@@ -1277,6 +1348,402 @@
         <v>40</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>هاتف ذكي Pro</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>هاتف ذكي بشاشة كبيرة وكاميرا ممتازة</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=701</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=702 | https://picsum.photos/400/400?random=703</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>إلكترونيات</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>جديد</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>📱 الأحدث</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>شاشة 6.7 بوصة | كاميرا 108MP | بطارية 5000mAh</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000mAh</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك سريع الشحن بسعة كبيرة</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=801</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=802</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>إكسسوارات</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>جديد</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>🔋 سعة كبيرة</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>سعة 20000mAh | شحن سريع | منفذين</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>كابل USB-C</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>كابل USB-C متين وطويل</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=901</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=902</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>إكسسوارات</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>جديد</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>🔌 متين</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>طول 2 متر | شحن سريع | متين</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>جراب موبايل</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>جراب حماية أنيق للموبايل</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=1001</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=1002</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>إكسسوارات</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>جديد</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>🛡️ حماية</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>مادة سيليكون | حماية من الصدمات</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>تيشيرت قطني</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>تيشيرت قطني مريح بألوان متعددة</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=1101</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=1102</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>ملابس</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>جديد</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>👕 مريح</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>قطن 100% | مقاسات متعددة | ألوان متنوعة</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>جاكيت شتوي</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>جاكيت شتوي دافئ وأنيق</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=1201</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>https://picsum.photos/400/400?random=1202</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>ملابس</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>عرض خاص</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>🧥 دافئ</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>خامة عالية | دافئ | مقاسات متعددة</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1288,11 +1755,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1322,24 +1789,36 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>ملابس</t>
+          <t>إكسسوارات</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>fas fa-tshirt</t>
+          <t>fas fa-gem</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>إكسسوارات</t>
+          <t>ملابس</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>fas fa-gem</t>
+          <t>fas fa-tshirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>كتب</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>fas fa-book</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1445,7 +1924,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/example</t>
+          <t>https://youtu.be/example1</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1464,6 +1943,68 @@
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1770051311270</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>شرح أساسيات التسويق الإلكتروني</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>https://youtu.be/example2</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>تسويق</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>0:45:00</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1770051311271</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>دورة تصميم الجرافيك للمبتدئين</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>https://youtu.be/example3</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>تصميم</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>1:00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1476,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1534,6 +2075,52 @@
       </c>
       <c r="E2" s="6" t="n">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>SAVE10</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>WELCOME</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -1642,14 +2229,10 @@
           <t>ticker</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>عرض خاص هذا الأسبوع - خصم 20% على المعالجات!</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>شريط الأخبار السفلي</t>
+          <t>شريط الأخبار (اختياري - الأفضل استخدام ورقة Notifications)</t>
         </is>
       </c>
     </row>
@@ -1659,14 +2242,10 @@
           <t>proof</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>نحن متخصصون في بيع الإلكترونيات والتكنولوجيا منذ 2020</t>
-        </is>
-      </c>
+      <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>رسالة إشعار الشراء (افصل بين رسائل متعددة بـ ,)</t>
+          <t>رسالة إشعار الشراء (اختياري - الأفضل استخدام ورقة Notifications)</t>
         </is>
       </c>
     </row>
@@ -1681,7 +2260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1775,16 +2354,16 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>أحمد من القاهرة اشترى رسيفر سيناتور 🔥</t>
+          <t>🎁 خصم 15% على الإكسسوارات حتى نهاية الشهر</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>proof</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -1795,16 +2374,16 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>محمد من المنصورة طلب قطعة واي فاي ⚡</t>
+          <t>⚡ وصل حديثاً: ساعة ذكية Ultra - اطلبها الآن</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>proof</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -1815,16 +2394,16 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>خالد من طنطا انضم للأكاديمية الآن ✅</t>
+          <t>📦 توصيل سريع لجميع المحافظات خلال 48 ساعة</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>proof</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -1835,7 +2414,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>عميل جديد طلب وصلة HDMI أصلية 🔌</t>
+          <t>أحمد من القاهرة اشترى رسيفر سيناتور 🔥</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1855,7 +2434,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>تم شحن طلب جديد إلى الإسكندرية بنجاح 🚚</t>
+          <t>محمد من المنصورة طلب قطعة واي فاي ⚡</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1867,6 +2446,126 @@
         <v>4</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>خالد من طنطا انضم للأكاديمية الآن ✅</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>proof</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>عميل جديد طلب وصلة HDMI أصلية 🔌</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>proof</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>تم شحن طلب جديد إلى الإسكندرية بنجاح 🚚</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>proof</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>سارة من الجيزة اشترت ساعة ذكية Ultra ⌚</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>proof</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>مصطفى من أسيوط طلب باور بانك 🔋</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>proof</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>تم توصيل طلب إلى المنصورة بنجاح ✅</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>proof</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1883,7 +2582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1910,6 +2609,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>الأكثر مبيعاً</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
